--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Pesa pubblica.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Pesa pubblica.xlsx
@@ -139,7 +139,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Info e orari pesa pubblica</t>
+    <t>Vai alle informazioni</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -338,7 +338,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
